--- a/Backend/Input/ADP/Monitoreo ADP - Nivel I.xlsx
+++ b/Backend/Input/ADP/Monitoreo ADP - Nivel I.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaquin.astorga\mis_proyectos\Proyecto ARMM\APP\Backend\Input\ADP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mineduca.sharepoint.com/sites/PCG/Documentos compartidos/Reporte mensual -ATMM/ADP/Nivel I/2025/Abril/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DF4DBC-D6B0-4E72-A37B-F51512034173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="144" documentId="8_{50EE1512-5B22-4D40-BDDF-5CEBD82B5728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C1F4DD6-C869-4BB9-821E-7D45BDCF8A23}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A0AD951-A275-4FB5-B4BD-A57A3ECB8FBA}"/>
+    <workbookView xWindow="-28920" yWindow="-4830" windowWidth="29040" windowHeight="15840" xr2:uid="{4A0AD951-A275-4FB5-B4BD-A57A3ECB8FBA}"/>
   </bookViews>
   <sheets>
     <sheet name="Fechas y comentarios" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
   <si>
     <t>Servicio</t>
   </si>
@@ -83,25 +83,31 @@
     <t>Superintendencia de Educación Superior</t>
   </si>
   <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
     <t>Comentarios</t>
   </si>
   <si>
     <t>En enero 2025 se envió mediante mail del Jefe del Gabinete del Ministro, el resultado del monitoreo del tercer año de gestión.</t>
   </si>
   <si>
-    <t>En enero 2025 se tramitó totalmente el acto administrativo que aprueba el grado de cumplimiento global de las metas del convenio del 2do año de gestión.</t>
-  </si>
-  <si>
-    <t>En febrero 2025 se tramitó totalmente el acto administrativo que aprueba el grado de cumplimiento global de las metas del convenio del 2do año de gestión.</t>
-  </si>
-  <si>
-    <t>En marzo 2025 se inició el monitoreo del primer año de gestión.</t>
+    <t>Actualizado al 06.05.25</t>
   </si>
   <si>
     <t>En marzo 2025 se envió mediante mail del Jefe del Gabinete del Ministro, el resultado del monitoreo del tercer año de gestión.</t>
   </si>
   <si>
-    <t>En marzo 2025 se enviaron los antecedentes a la División Jurídica para la elaboración del acto administrativo de la evaluación del segundo año de gestión.</t>
+    <t>En enero 2025 se tramitó totalmente el acto administrativo que aprueba el grado de cumplimiento global de las metas del convenio del segundo año de gestión.</t>
+  </si>
+  <si>
+    <t>En abril 2025 se envió mediante mail del Jefe del Gabinete del Ministro, el resultado del monitoreo del primer año de gestión.</t>
+  </si>
+  <si>
+    <t>En febrero 2025 se tramitó totalmente el acto administrativo que aprueba el grado de cumplimiento global de las metas del convenio del segundo año de gestión.</t>
+  </si>
+  <si>
+    <t>En abril 2025 se tramitó totalmente el acto administrativo que aprueba el grado de cumplimiento global de las metas del convenio del segundo año de gestión.</t>
   </si>
 </sst>
 </file>
@@ -149,22 +155,23 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="18"/>
-      <color theme="0"/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
       <name val="Calibri Light"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri Light"/>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri Light"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -194,12 +201,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDAF2D0"/>
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -214,7 +221,9 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -224,24 +233,18 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
+      <left/>
+      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -250,74 +253,17 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -326,7 +272,7 @@
       </left>
       <right/>
       <top style="medium">
-        <color theme="1"/>
+        <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -339,7 +285,7 @@
         <color theme="0"/>
       </right>
       <top style="medium">
-        <color theme="1"/>
+        <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -349,26 +295,41 @@
         <color theme="0"/>
       </left>
       <right style="medium">
-        <color theme="1"/>
+        <color indexed="64"/>
       </right>
       <top style="medium">
-        <color theme="1"/>
+        <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
       </left>
       <right style="medium">
-        <color theme="1"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -379,7 +340,7 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -388,58 +349,28 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="1"/>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -448,53 +379,41 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="14" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -830,11 +749,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0C29CBF-8F22-456D-B3FB-D5E8EA4BA277}">
-  <dimension ref="B3:I23"/>
+  <dimension ref="B3:I21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="52" customWidth="1"/>
-    <col min="3" max="3" width="37.7109375" customWidth="1"/>
+    <col min="3" max="3" width="36.7109375" customWidth="1"/>
     <col min="4" max="4" width="25.42578125" customWidth="1"/>
     <col min="5" max="5" width="25.85546875" customWidth="1"/>
     <col min="6" max="6" width="24.140625" customWidth="1"/>
@@ -844,289 +763,332 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="2:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="16" t="s">
+    <row r="4" spans="2:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="20" t="s">
+      <c r="I4" s="10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="5">
         <v>44725</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="5">
         <v>44908</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="5">
         <v>45090</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="5">
         <v>45273</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="5">
         <v>45456</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="5">
         <v>45639</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="11">
         <v>45821</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="8">
-        <v>44789</v>
-      </c>
-      <c r="D6" s="8">
+      <c r="C6" s="5">
+        <v>37484</v>
+      </c>
+      <c r="D6" s="5">
         <v>44608</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="5">
         <v>45154</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="5">
         <v>45338</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="5">
         <v>45520</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="7">
         <v>45704</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="11">
         <v>45885</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="5">
         <v>44868</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="5">
         <v>45049</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="5">
         <v>45233</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="5">
         <v>45415</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="7">
         <v>45599</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="6">
         <v>45780</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="11">
         <v>45964</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="5">
         <v>45439</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="5">
         <v>45623</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="6">
         <v>45804</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="6">
         <v>45988</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="6">
         <v>46169</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="6">
         <v>46353</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="11">
         <v>46534</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="5">
         <v>44900</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="5">
         <v>45082</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="5">
         <v>45265</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="5">
         <v>45448</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="5">
         <v>45631</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="6">
         <v>45813</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="11">
         <v>45813</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="5">
         <v>44930</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="5">
         <v>45111</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="5">
         <v>45295</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="5">
         <v>45477</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="5">
         <v>45661</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="6">
         <v>45842</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="11">
         <v>46026</v>
       </c>
     </row>
     <row r="11" spans="2:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="5">
         <v>44958</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="5">
         <v>45139</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="5">
         <v>45323</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="5">
         <v>45505</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="7">
         <v>45689</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="6">
         <v>45870</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I11" s="11">
         <v>46054</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="2:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
+    <row r="13" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" ht="108.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="15"/>
+      <c r="E15" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="2:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="15"/>
+      <c r="E16" s="18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="125.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="5"/>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" spans="2:6" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="17" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="2:6" ht="125.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="2" t="s">
+      <c r="D17" s="15"/>
+      <c r="E17" s="18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="24" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="2" t="s">
+      <c r="C18" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="15"/>
+      <c r="E18" s="18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C19" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="15"/>
+      <c r="E19" s="18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="2:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="2" t="s">
+    <row r="20" spans="2:5" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C20" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="15"/>
+      <c r="E20" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="6"/>
-    </row>
-    <row r="23" spans="2:6" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="B23" s="2" t="s">
+    </row>
+    <row r="21" spans="2:5" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="25" t="s">
-        <v>21</v>
+      <c r="C21" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="15"/>
+      <c r="E21" s="18" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
+    <orden xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010039E554BA5E2FA5449283D399C0FD5B7C" ma:contentTypeVersion="22" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="99316247900046118e13a249c2e2a979">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xmlns:ns3="954542bb-2825-439d-9db6-a5c04d3b21fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="18ff31ee8df8f768b70ea272e17d0ebc" ns2:_="" ns3:_="">
     <xsd:import namespace="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
@@ -1390,7 +1352,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1399,19 +1361,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
-    <orden xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CD7FD21-EF15-47EF-BE64-355A321DA262}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
+    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{070F46FF-6A46-467B-9374-33A76BCB1EEF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1430,21 +1391,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E56B48B9-8D50-4C8A-A3A8-779F015C9076}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CD7FD21-EF15-47EF-BE64-355A321DA262}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
-    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Backend/Input/ADP/Monitoreo ADP - Nivel I.xlsx
+++ b/Backend/Input/ADP/Monitoreo ADP - Nivel I.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mineduca.sharepoint.com/sites/PCG/Documentos compartidos/Reporte mensual -ATMM/ADP/Nivel I/2025/Abril/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mineduca.sharepoint.com/sites/PCG/Documentos compartidos/Reporte mensual -ATMM/ADP/Nivel I/2025/Mayo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="144" documentId="8_{50EE1512-5B22-4D40-BDDF-5CEBD82B5728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C1F4DD6-C869-4BB9-821E-7D45BDCF8A23}"/>
+  <xr:revisionPtr revIDLastSave="198" documentId="8_{50EE1512-5B22-4D40-BDDF-5CEBD82B5728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{058233BB-EDA1-4860-BF84-2C76331E3007}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-4830" windowWidth="29040" windowHeight="15840" xr2:uid="{4A0AD951-A275-4FB5-B4BD-A57A3ECB8FBA}"/>
+    <workbookView xWindow="20370" yWindow="-3945" windowWidth="29040" windowHeight="15840" xr2:uid="{4A0AD951-A275-4FB5-B4BD-A57A3ECB8FBA}"/>
   </bookViews>
   <sheets>
     <sheet name="Fechas y comentarios" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="26">
   <si>
     <t>Servicio</t>
   </si>
@@ -83,9 +83,6 @@
     <t>Superintendencia de Educación Superior</t>
   </si>
   <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
     <t>Comentarios</t>
   </si>
   <si>
@@ -98,16 +95,26 @@
     <t>En marzo 2025 se envió mediante mail del Jefe del Gabinete del Ministro, el resultado del monitoreo del tercer año de gestión.</t>
   </si>
   <si>
-    <t>En enero 2025 se tramitó totalmente el acto administrativo que aprueba el grado de cumplimiento global de las metas del convenio del segundo año de gestión.</t>
-  </si>
-  <si>
-    <t>En abril 2025 se envió mediante mail del Jefe del Gabinete del Ministro, el resultado del monitoreo del primer año de gestión.</t>
-  </si>
-  <si>
     <t>En febrero 2025 se tramitó totalmente el acto administrativo que aprueba el grado de cumplimiento global de las metas del convenio del segundo año de gestión.</t>
   </si>
   <si>
     <t>En abril 2025 se tramitó totalmente el acto administrativo que aprueba el grado de cumplimiento global de las metas del convenio del segundo año de gestión.</t>
+  </si>
+  <si>
+    <t>MAYO</t>
+  </si>
+  <si>
+    <t>Actualizado al 03.06.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En mayo 2025 se inició el monitoreo del tercer año de gestión
+</t>
+  </si>
+  <si>
+    <t>En mayo 2025 se inició el proceso de evaluación del primer año de gestión.</t>
+  </si>
+  <si>
+    <t>En mayo 2025 se envió a tramitación el acto administrativo que aprueba el grado de cumplimiento global de las metas del convenio del segundo año de gestión.</t>
   </si>
 </sst>
 </file>
@@ -168,7 +175,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -413,7 +419,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -753,7 +759,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="52" customWidth="1"/>
-    <col min="3" max="3" width="36.7109375" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" customWidth="1"/>
     <col min="4" max="4" width="25.42578125" customWidth="1"/>
     <col min="5" max="5" width="25.85546875" customWidth="1"/>
     <col min="6" max="6" width="24.140625" customWidth="1"/>
@@ -860,7 +866,7 @@
       <c r="G7" s="7">
         <v>45599</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="7">
         <v>45780</v>
       </c>
       <c r="I7" s="11">
@@ -877,7 +883,7 @@
       <c r="D8" s="5">
         <v>45623</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <v>45804</v>
       </c>
       <c r="F8" s="6">
@@ -898,25 +904,25 @@
         <v>12</v>
       </c>
       <c r="C9" s="5">
-        <v>44900</v>
+        <v>45017</v>
       </c>
       <c r="D9" s="5">
-        <v>45082</v>
+        <v>45200</v>
       </c>
       <c r="E9" s="5">
-        <v>45265</v>
+        <v>45383</v>
       </c>
       <c r="F9" s="5">
-        <v>45448</v>
+        <v>45566</v>
       </c>
       <c r="G9" s="5">
-        <v>45631</v>
+        <v>45748</v>
       </c>
       <c r="H9" s="6">
-        <v>45813</v>
+        <v>45931</v>
       </c>
       <c r="I9" s="11">
-        <v>45813</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="21" x14ac:dyDescent="0.25">
@@ -973,7 +979,7 @@
     </row>
     <row r="13" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C13" s="16" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="2:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -981,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -989,11 +995,11 @@
         <v>8</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="18" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F15" s="4"/>
     </row>
@@ -1002,71 +1008,71 @@
         <v>9</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D16" s="15"/>
       <c r="E16" s="18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" ht="125.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="56.25" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D17" s="15"/>
       <c r="E17" s="18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" ht="93.75" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="37.5" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D18" s="15"/>
       <c r="E18" s="18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" ht="112.5" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="93.75" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" ht="112.5" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="93.75" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D20" s="15"/>
       <c r="E20" s="18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" ht="112.5" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="93.75" x14ac:dyDescent="0.25">
       <c r="B21" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="18" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Backend/Input/ADP/Monitoreo ADP - Nivel I.xlsx
+++ b/Backend/Input/ADP/Monitoreo ADP - Nivel I.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mineduca.sharepoint.com/sites/PCG/Documentos compartidos/Reporte mensual -ATMM/ADP/Nivel I/2025/Mayo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mineduca.sharepoint.com/sites/PCG/Documentos compartidos/Reporte mensual -ARMM/ADP/Nivel I/2025/Junio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="198" documentId="8_{50EE1512-5B22-4D40-BDDF-5CEBD82B5728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{058233BB-EDA1-4860-BF84-2C76331E3007}"/>
+  <xr:revisionPtr revIDLastSave="247" documentId="8_{50EE1512-5B22-4D40-BDDF-5CEBD82B5728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2BB265B-743F-4651-BE7A-6018B66B9999}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-3945" windowWidth="29040" windowHeight="15840" xr2:uid="{4A0AD951-A275-4FB5-B4BD-A57A3ECB8FBA}"/>
+    <workbookView xWindow="-28920" yWindow="-4830" windowWidth="29040" windowHeight="15840" xr2:uid="{4A0AD951-A275-4FB5-B4BD-A57A3ECB8FBA}"/>
   </bookViews>
   <sheets>
     <sheet name="Fechas y comentarios" sheetId="1" r:id="rId1"/>
@@ -36,14 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="25">
   <si>
     <t>Servicio</t>
   </si>
   <si>
-    <t>Convenio totalmente tramitado</t>
-  </si>
-  <si>
     <t>Monitoreo Año 1</t>
   </si>
   <si>
@@ -53,9 +50,6 @@
     <t>Monitoreo Año 2</t>
   </si>
   <si>
-    <t>Evaluacion Año 2</t>
-  </si>
-  <si>
     <t>Monitoreo Año 3</t>
   </si>
   <si>
@@ -86,12 +80,6 @@
     <t>Comentarios</t>
   </si>
   <si>
-    <t>En enero 2025 se envió mediante mail del Jefe del Gabinete del Ministro, el resultado del monitoreo del tercer año de gestión.</t>
-  </si>
-  <si>
-    <t>Actualizado al 06.05.25</t>
-  </si>
-  <si>
     <t>En marzo 2025 se envió mediante mail del Jefe del Gabinete del Ministro, el resultado del monitoreo del tercer año de gestión.</t>
   </si>
   <si>
@@ -101,20 +89,32 @@
     <t>En abril 2025 se tramitó totalmente el acto administrativo que aprueba el grado de cumplimiento global de las metas del convenio del segundo año de gestión.</t>
   </si>
   <si>
-    <t>MAYO</t>
-  </si>
-  <si>
-    <t>Actualizado al 03.06.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En mayo 2025 se inició el monitoreo del tercer año de gestión
+    <t>En mayo 2025 se inició el proceso de evaluación del primer año de gestión.</t>
+  </si>
+  <si>
+    <t>Fecha nombramiento</t>
+  </si>
+  <si>
+    <t>JUNIO</t>
+  </si>
+  <si>
+    <t>Actualizado al 08.07.25</t>
+  </si>
+  <si>
+    <t>Evaluación:
+En junio 2025 se inició el proceso de evaluación del tercer año de gestión
+Formulación:
+Ministro renueva nombramiento de la Secretaria General, por lo que en junio 2025 se inició el proceso de formulación del convenio del segundo periodo gestión.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En junio 2025 se envió mediante mail del Jefe del Gabinete del Ministro, el resultado del monitoreo del tercer año de gestión.
 </t>
   </si>
   <si>
-    <t>En mayo 2025 se inició el proceso de evaluación del primer año de gestión.</t>
-  </si>
-  <si>
-    <t>En mayo 2025 se envió a tramitación el acto administrativo que aprueba el grado de cumplimiento global de las metas del convenio del segundo año de gestión.</t>
+    <t>En junio 2025 se tramitó totalmente el acto administrativo que aprueba el grado de cumplimiento global de las metas del convenio del segundo año de gestión.</t>
+  </si>
+  <si>
+    <t>Evaluación Año 2</t>
   </si>
 </sst>
 </file>
@@ -180,7 +180,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -190,12 +190,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F0D9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -367,7 +361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -379,15 +373,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="14" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -412,14 +403,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -755,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0C29CBF-8F22-456D-B3FB-D5E8EA4BA277}">
-  <dimension ref="B3:I21"/>
+  <dimension ref="B3:I22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="52" customWidth="1"/>
@@ -774,305 +774,331 @@
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="I4" s="9" t="s">
         <v>5</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="21" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="5">
+        <v>6</v>
+      </c>
+      <c r="C5" s="6">
         <v>44725</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="6">
         <v>44908</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="6">
         <v>45090</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="6">
         <v>45273</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="6">
         <v>45456</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="6">
         <v>45639</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="20">
         <v>45821</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="21" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="5">
-        <v>37484</v>
-      </c>
-      <c r="D6" s="5">
-        <v>44608</v>
-      </c>
-      <c r="E6" s="5">
-        <v>45154</v>
-      </c>
-      <c r="F6" s="5">
-        <v>45338</v>
-      </c>
-      <c r="G6" s="5">
-        <v>45520</v>
-      </c>
-      <c r="H6" s="7">
-        <v>45704</v>
-      </c>
-      <c r="I6" s="11">
-        <v>45885</v>
+        <v>6</v>
+      </c>
+      <c r="C6" s="6">
+        <v>45822</v>
+      </c>
+      <c r="D6" s="17">
+        <v>46005</v>
+      </c>
+      <c r="E6" s="17">
+        <v>46187</v>
+      </c>
+      <c r="F6" s="17">
+        <v>46370</v>
+      </c>
+      <c r="G6" s="17">
+        <v>46552</v>
+      </c>
+      <c r="H6" s="17">
+        <v>46735</v>
+      </c>
+      <c r="I6" s="10">
+        <v>46918</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="21" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="5">
-        <v>44868</v>
-      </c>
-      <c r="D7" s="5">
-        <v>45049</v>
-      </c>
-      <c r="E7" s="5">
-        <v>45233</v>
-      </c>
-      <c r="F7" s="5">
-        <v>45415</v>
-      </c>
-      <c r="G7" s="7">
-        <v>45599</v>
-      </c>
-      <c r="H7" s="7">
-        <v>45780</v>
-      </c>
-      <c r="I7" s="11">
-        <v>45964</v>
+        <v>7</v>
+      </c>
+      <c r="C7" s="6">
+        <v>37484</v>
+      </c>
+      <c r="D7" s="6">
+        <v>44608</v>
+      </c>
+      <c r="E7" s="6">
+        <v>45154</v>
+      </c>
+      <c r="F7" s="6">
+        <v>45338</v>
+      </c>
+      <c r="G7" s="6">
+        <v>45520</v>
+      </c>
+      <c r="H7" s="6">
+        <v>45704</v>
+      </c>
+      <c r="I7" s="10">
+        <v>45885</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="21" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="5">
-        <v>45439</v>
-      </c>
-      <c r="D8" s="5">
-        <v>45623</v>
-      </c>
-      <c r="E8" s="5">
-        <v>45804</v>
+        <v>8</v>
+      </c>
+      <c r="C8" s="6">
+        <v>44868</v>
+      </c>
+      <c r="D8" s="6">
+        <v>45049</v>
+      </c>
+      <c r="E8" s="6">
+        <v>45233</v>
       </c>
       <c r="F8" s="6">
-        <v>45988</v>
+        <v>45415</v>
       </c>
       <c r="G8" s="6">
-        <v>46169</v>
+        <v>45599</v>
       </c>
       <c r="H8" s="6">
-        <v>46353</v>
-      </c>
-      <c r="I8" s="11">
-        <v>46534</v>
+        <v>45780</v>
+      </c>
+      <c r="I8" s="10">
+        <v>45964</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="21" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="5">
-        <v>45017</v>
-      </c>
-      <c r="D9" s="5">
-        <v>45200</v>
-      </c>
-      <c r="E9" s="5">
-        <v>45383</v>
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>45439</v>
+      </c>
+      <c r="D9" s="6">
+        <v>45623</v>
+      </c>
+      <c r="E9" s="6">
+        <v>45804</v>
       </c>
       <c r="F9" s="5">
-        <v>45566</v>
+        <v>45988</v>
       </c>
       <c r="G9" s="5">
-        <v>45748</v>
-      </c>
-      <c r="H9" s="6">
-        <v>45931</v>
-      </c>
-      <c r="I9" s="11">
-        <v>46113</v>
+        <v>46169</v>
+      </c>
+      <c r="H9" s="5">
+        <v>46353</v>
+      </c>
+      <c r="I9" s="10">
+        <v>46534</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="21" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="6">
+        <v>45017</v>
+      </c>
+      <c r="D10" s="6">
+        <v>45200</v>
+      </c>
+      <c r="E10" s="6">
+        <v>45383</v>
+      </c>
+      <c r="F10" s="6">
+        <v>45566</v>
+      </c>
+      <c r="G10" s="6">
+        <v>45748</v>
+      </c>
+      <c r="H10" s="5">
+        <v>45931</v>
+      </c>
+      <c r="I10" s="10">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="6">
+        <v>44930</v>
+      </c>
+      <c r="D11" s="6">
+        <v>45111</v>
+      </c>
+      <c r="E11" s="6">
+        <v>45295</v>
+      </c>
+      <c r="F11" s="6">
+        <v>45477</v>
+      </c>
+      <c r="G11" s="6">
+        <v>45661</v>
+      </c>
+      <c r="H11" s="5">
+        <v>45842</v>
+      </c>
+      <c r="I11" s="10">
+        <v>46026</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="6">
+        <v>44958</v>
+      </c>
+      <c r="D12" s="6">
+        <v>45139</v>
+      </c>
+      <c r="E12" s="6">
+        <v>45323</v>
+      </c>
+      <c r="F12" s="6">
+        <v>45505</v>
+      </c>
+      <c r="G12" s="6">
+        <v>45689</v>
+      </c>
+      <c r="H12" s="5">
+        <v>45870</v>
+      </c>
+      <c r="I12" s="10">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="5">
-        <v>44930</v>
-      </c>
-      <c r="D10" s="5">
-        <v>45111</v>
-      </c>
-      <c r="E10" s="5">
-        <v>45295</v>
-      </c>
-      <c r="F10" s="5">
-        <v>45477</v>
-      </c>
-      <c r="G10" s="5">
-        <v>45661</v>
-      </c>
-      <c r="H10" s="6">
-        <v>45842</v>
-      </c>
-      <c r="I10" s="11">
-        <v>46026</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="12" t="s">
+    </row>
+    <row r="16" spans="2:9" ht="183" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="14"/>
+      <c r="E16" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="2:5" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="5">
-        <v>44958</v>
-      </c>
-      <c r="D11" s="5">
-        <v>45139</v>
-      </c>
-      <c r="E11" s="5">
-        <v>45323</v>
-      </c>
-      <c r="F11" s="5">
-        <v>45505</v>
-      </c>
-      <c r="G11" s="7">
-        <v>45689</v>
-      </c>
-      <c r="H11" s="6">
-        <v>45870</v>
-      </c>
-      <c r="I11" s="11">
-        <v>46054</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="1" t="s">
+      <c r="D17" s="14"/>
+      <c r="E17" s="19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="18" t="s">
+      <c r="C18" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="2:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="1" t="s">
+      <c r="D18" s="14"/>
+      <c r="E18" s="19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="18" t="s">
+      <c r="C19" s="16" t="s">
         <v>17</v>
+      </c>
+      <c r="D19" s="14"/>
+      <c r="E19" s="19" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="93.75" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="18" t="s">
-        <v>22</v>
+        <v>10</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="14"/>
+      <c r="E20" s="19" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="B21" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="17" t="s">
+      <c r="B21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="14"/>
+      <c r="E21" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="15"/>
-      <c r="E21" s="18" t="s">
-        <v>22</v>
+    </row>
+    <row r="22" spans="2:5" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="14"/>
+      <c r="E22" s="19" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
